--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-allergyintolerance.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-allergyintolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T12:03:31+00:00</t>
+    <t>2026-02-04T14:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -773,7 +773,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -796,7 +796,7 @@
 Informant</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole)
 </t>
   </si>
   <si>
@@ -1361,7 +1361,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="182.5078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-allergyintolerance.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-allergyintolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T14:21:15+00:00</t>
+    <t>2026-02-04T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-allergyintolerance.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-allergyintolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T15:46:20+00:00</t>
+    <t>2026-02-05T06:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-allergyintolerance.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-allergyintolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T06:51:53+00:00</t>
+    <t>2026-02-05T08:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-allergyintolerance.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-allergyintolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T08:33:30+00:00</t>
+    <t>2026-02-05T09:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-allergyintolerance.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-allergyintolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:19:21+00:00</t>
+    <t>2026-02-05T09:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
